--- a/data/industry/CFM/OEM SSD.xlsx
+++ b/data/industry/CFM/OEM SSD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B548AF-7E99-42C6-9434-831833C40DAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AF2EEC-F6E5-43D8-AAFD-695227F0AFA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OEM SSD 256GB SATA" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -74,11 +74,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -139,7 +140,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -171,6 +172,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -452,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -1093,7 +1098,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -1106,6 +1111,121 @@
       </c>
       <c r="G28" s="12">
         <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>54</v>
+      </c>
+      <c r="F29" s="12">
+        <v>58</v>
+      </c>
+      <c r="G29" s="12">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>54</v>
+      </c>
+      <c r="F30" s="12">
+        <v>58</v>
+      </c>
+      <c r="G30" s="12">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>54</v>
+      </c>
+      <c r="F31" s="12">
+        <v>58</v>
+      </c>
+      <c r="G31" s="12">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>55</v>
+      </c>
+      <c r="F32" s="12">
+        <v>59</v>
+      </c>
+      <c r="G32" s="12">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>58</v>
+      </c>
+      <c r="F33" s="12">
+        <v>62</v>
+      </c>
+      <c r="G33" s="12">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1116,7 +1236,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F473D36E-208F-4614-83B5-69AB6F33294E}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -1757,7 +1877,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -1770,6 +1890,121 @@
       </c>
       <c r="G28" s="12">
         <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>95</v>
+      </c>
+      <c r="F29" s="12">
+        <v>102</v>
+      </c>
+      <c r="G29" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>95</v>
+      </c>
+      <c r="F30" s="12">
+        <v>102</v>
+      </c>
+      <c r="G30" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>95</v>
+      </c>
+      <c r="F31" s="12">
+        <v>102</v>
+      </c>
+      <c r="G31" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>97</v>
+      </c>
+      <c r="F32" s="12">
+        <v>104</v>
+      </c>
+      <c r="G32" s="12">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>103</v>
+      </c>
+      <c r="F33" s="12">
+        <v>110</v>
+      </c>
+      <c r="G33" s="12">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1780,7 +2015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6C0178-E414-47B2-A630-84DA7232A61F}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -2421,7 +2656,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -2434,6 +2669,121 @@
       </c>
       <c r="G28" s="12">
         <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>188</v>
+      </c>
+      <c r="F29" s="12">
+        <v>192</v>
+      </c>
+      <c r="G29" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>188</v>
+      </c>
+      <c r="F30" s="12">
+        <v>192</v>
+      </c>
+      <c r="G30" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>188</v>
+      </c>
+      <c r="F31" s="12">
+        <v>192</v>
+      </c>
+      <c r="G31" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>188</v>
+      </c>
+      <c r="F32" s="12">
+        <v>192</v>
+      </c>
+      <c r="G32" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>188</v>
+      </c>
+      <c r="F33" s="12">
+        <v>192</v>
+      </c>
+      <c r="G33" s="12">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2794,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE21688-DF7E-4F8C-887E-342649A09FB0}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -3085,7 +3435,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -3098,6 +3448,121 @@
       </c>
       <c r="G28" s="12">
         <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>55.5</v>
+      </c>
+      <c r="F29" s="12">
+        <v>58</v>
+      </c>
+      <c r="G29" s="12">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>55.5</v>
+      </c>
+      <c r="F30" s="12">
+        <v>58</v>
+      </c>
+      <c r="G30" s="12">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>55.5</v>
+      </c>
+      <c r="F31" s="12">
+        <v>58</v>
+      </c>
+      <c r="G31" s="12">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>56.5</v>
+      </c>
+      <c r="F32" s="12">
+        <v>59</v>
+      </c>
+      <c r="G32" s="12">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>58.5</v>
+      </c>
+      <c r="F33" s="12">
+        <v>61</v>
+      </c>
+      <c r="G33" s="12">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3108,7 +3573,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{075E49D7-A50C-4EF3-8D98-3E3352C23834}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -3749,7 +4214,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -3762,6 +4227,121 @@
       </c>
       <c r="G28" s="12">
         <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>99.5</v>
+      </c>
+      <c r="F29" s="12">
+        <v>105</v>
+      </c>
+      <c r="G29" s="12">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>99.5</v>
+      </c>
+      <c r="F30" s="12">
+        <v>105</v>
+      </c>
+      <c r="G30" s="12">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>99.5</v>
+      </c>
+      <c r="F31" s="12">
+        <v>105</v>
+      </c>
+      <c r="G31" s="12">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>102.5</v>
+      </c>
+      <c r="F32" s="12">
+        <v>108</v>
+      </c>
+      <c r="G32" s="12">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>106.5</v>
+      </c>
+      <c r="F33" s="12">
+        <v>112</v>
+      </c>
+      <c r="G33" s="12">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3772,7 +4352,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18515E64-A7B9-4EA8-8571-9A16CD6B2FD3}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -4413,7 +4993,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -4426,6 +5006,121 @@
       </c>
       <c r="G28" s="12">
         <v>185</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>189</v>
+      </c>
+      <c r="F29" s="12">
+        <v>192</v>
+      </c>
+      <c r="G29" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>189</v>
+      </c>
+      <c r="F30" s="12">
+        <v>192</v>
+      </c>
+      <c r="G30" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>189</v>
+      </c>
+      <c r="F31" s="12">
+        <v>192</v>
+      </c>
+      <c r="G31" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>189</v>
+      </c>
+      <c r="F32" s="12">
+        <v>192</v>
+      </c>
+      <c r="G32" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>189</v>
+      </c>
+      <c r="F33" s="12">
+        <v>192</v>
+      </c>
+      <c r="G33" s="12">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -4436,7 +5131,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8286ED8B-68EC-4D79-8787-976F03BA0C32}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -5077,7 +5772,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -5090,6 +5785,121 @@
       </c>
       <c r="G28" s="12">
         <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>108</v>
+      </c>
+      <c r="F29" s="12">
+        <v>112</v>
+      </c>
+      <c r="G29" s="12">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>108</v>
+      </c>
+      <c r="F30" s="12">
+        <v>112</v>
+      </c>
+      <c r="G30" s="12">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>108</v>
+      </c>
+      <c r="F31" s="12">
+        <v>112</v>
+      </c>
+      <c r="G31" s="12">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>110</v>
+      </c>
+      <c r="F32" s="12">
+        <v>114</v>
+      </c>
+      <c r="G32" s="12">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>113</v>
+      </c>
+      <c r="F33" s="12">
+        <v>117</v>
+      </c>
+      <c r="G33" s="12">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -5100,7 +5910,786 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62752974-E8DF-439D-ACF9-ECD10A65F3F8}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="14"/>
+    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="6">
+        <v>45860</v>
+      </c>
+      <c r="B2" s="6">
+        <v>45860</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="14">
+        <v>57</v>
+      </c>
+      <c r="F2" s="14">
+        <v>60</v>
+      </c>
+      <c r="G2" s="14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="6">
+        <v>45867</v>
+      </c>
+      <c r="B3" s="6">
+        <v>45867</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="14">
+        <v>57</v>
+      </c>
+      <c r="F3" s="14">
+        <v>60</v>
+      </c>
+      <c r="G3" s="14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="6">
+        <v>45874</v>
+      </c>
+      <c r="B4" s="6">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="14">
+        <v>57</v>
+      </c>
+      <c r="F4" s="14">
+        <v>60</v>
+      </c>
+      <c r="G4" s="14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>45881</v>
+      </c>
+      <c r="B5" s="6">
+        <v>45881</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="14">
+        <v>57</v>
+      </c>
+      <c r="F5" s="14">
+        <v>60</v>
+      </c>
+      <c r="G5" s="14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
+        <v>45888</v>
+      </c>
+      <c r="B6" s="6">
+        <v>45888</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="14">
+        <v>57</v>
+      </c>
+      <c r="F6" s="14">
+        <v>60</v>
+      </c>
+      <c r="G6" s="14">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>45895</v>
+      </c>
+      <c r="B7" s="6">
+        <v>45895</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="14">
+        <v>56</v>
+      </c>
+      <c r="F7" s="14">
+        <v>59</v>
+      </c>
+      <c r="G7" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>45902</v>
+      </c>
+      <c r="B8" s="6">
+        <v>45902</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="14">
+        <v>56</v>
+      </c>
+      <c r="F8" s="14">
+        <v>59</v>
+      </c>
+      <c r="G8" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>45909</v>
+      </c>
+      <c r="B9" s="6">
+        <v>45909</v>
+      </c>
+      <c r="C9" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="14">
+        <v>56</v>
+      </c>
+      <c r="F9" s="14">
+        <v>59</v>
+      </c>
+      <c r="G9" s="14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>45916</v>
+      </c>
+      <c r="B10" s="6">
+        <v>45916</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="14">
+        <v>59</v>
+      </c>
+      <c r="F10" s="14">
+        <v>62</v>
+      </c>
+      <c r="G10" s="14">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>45923</v>
+      </c>
+      <c r="B11" s="6">
+        <v>45923</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="14">
+        <v>59</v>
+      </c>
+      <c r="F11" s="14">
+        <v>62</v>
+      </c>
+      <c r="G11" s="14">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
+        <v>45930</v>
+      </c>
+      <c r="B12" s="6">
+        <v>45930</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="14">
+        <v>59</v>
+      </c>
+      <c r="F12" s="14">
+        <v>62</v>
+      </c>
+      <c r="G12" s="14">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>45944</v>
+      </c>
+      <c r="B13" s="6">
+        <v>45944</v>
+      </c>
+      <c r="C13" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="14">
+        <v>66.5</v>
+      </c>
+      <c r="F13" s="14">
+        <v>69.5</v>
+      </c>
+      <c r="G13" s="14">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="6">
+        <v>45951</v>
+      </c>
+      <c r="B14" s="6">
+        <v>45951</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="14">
+        <v>68</v>
+      </c>
+      <c r="F14" s="14">
+        <v>71</v>
+      </c>
+      <c r="G14" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="6">
+        <v>45958</v>
+      </c>
+      <c r="B15" s="6">
+        <v>45958</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="14">
+        <v>73</v>
+      </c>
+      <c r="F15" s="14">
+        <v>76</v>
+      </c>
+      <c r="G15" s="14">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
+        <v>45965</v>
+      </c>
+      <c r="B16" s="6">
+        <v>45965</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="14">
+        <v>79</v>
+      </c>
+      <c r="F16" s="14">
+        <v>82</v>
+      </c>
+      <c r="G16" s="14">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
+        <v>45972</v>
+      </c>
+      <c r="B17" s="6">
+        <v>45972</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="14">
+        <v>79</v>
+      </c>
+      <c r="F17" s="14">
+        <v>82</v>
+      </c>
+      <c r="G17" s="14">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
+        <v>45979</v>
+      </c>
+      <c r="B18" s="6">
+        <v>45979</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="14">
+        <v>88</v>
+      </c>
+      <c r="F18" s="14">
+        <v>91</v>
+      </c>
+      <c r="G18" s="14">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="6">
+        <v>45986</v>
+      </c>
+      <c r="B19" s="6">
+        <v>45986</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="14">
+        <v>103</v>
+      </c>
+      <c r="F19" s="14">
+        <v>106</v>
+      </c>
+      <c r="G19" s="14">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="6">
+        <v>45993</v>
+      </c>
+      <c r="B20" s="6">
+        <v>45993</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="14">
+        <v>123</v>
+      </c>
+      <c r="F20" s="14">
+        <v>126</v>
+      </c>
+      <c r="G20" s="14">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="6">
+        <v>46000</v>
+      </c>
+      <c r="B21" s="6">
+        <v>46000</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="14">
+        <v>133</v>
+      </c>
+      <c r="F21" s="14">
+        <v>136</v>
+      </c>
+      <c r="G21" s="14">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="6">
+        <v>46007</v>
+      </c>
+      <c r="B22" s="6">
+        <v>46007</v>
+      </c>
+      <c r="C22" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="14">
+        <v>133</v>
+      </c>
+      <c r="F22" s="14">
+        <v>136</v>
+      </c>
+      <c r="G22" s="14">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="6">
+        <v>46014</v>
+      </c>
+      <c r="B23" s="6">
+        <v>46014</v>
+      </c>
+      <c r="C23" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="14">
+        <v>133</v>
+      </c>
+      <c r="F23" s="14">
+        <v>136</v>
+      </c>
+      <c r="G23" s="14">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="6">
+        <v>46021</v>
+      </c>
+      <c r="B24" s="6">
+        <v>46021</v>
+      </c>
+      <c r="C24" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="14">
+        <v>133</v>
+      </c>
+      <c r="F24" s="14">
+        <v>136</v>
+      </c>
+      <c r="G24" s="14">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="6">
+        <v>46028</v>
+      </c>
+      <c r="B25" s="6">
+        <v>46028</v>
+      </c>
+      <c r="C25" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="14">
+        <v>146</v>
+      </c>
+      <c r="F25" s="14">
+        <v>149</v>
+      </c>
+      <c r="G25" s="14">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="10">
+        <v>46035</v>
+      </c>
+      <c r="B26" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C26" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="14">
+        <v>153</v>
+      </c>
+      <c r="F26" s="14">
+        <v>156</v>
+      </c>
+      <c r="G26" s="14">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="10">
+        <v>46042</v>
+      </c>
+      <c r="B27" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C27" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="14">
+        <v>198</v>
+      </c>
+      <c r="F27" s="14">
+        <v>201</v>
+      </c>
+      <c r="G27" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="6">
+        <v>46049</v>
+      </c>
+      <c r="B28" s="6">
+        <v>46049</v>
+      </c>
+      <c r="C28" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="14">
+        <v>198</v>
+      </c>
+      <c r="F28" s="14">
+        <v>201</v>
+      </c>
+      <c r="G28" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="14">
+        <v>198</v>
+      </c>
+      <c r="F29" s="14">
+        <v>201</v>
+      </c>
+      <c r="G29" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="14">
+        <v>198</v>
+      </c>
+      <c r="F30" s="14">
+        <v>201</v>
+      </c>
+      <c r="G30" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="14">
+        <v>198</v>
+      </c>
+      <c r="F31" s="14">
+        <v>201</v>
+      </c>
+      <c r="G31" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="14">
+        <v>198</v>
+      </c>
+      <c r="F32" s="14">
+        <v>201</v>
+      </c>
+      <c r="G32" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="14">
+        <v>198</v>
+      </c>
+      <c r="F33" s="14">
+        <v>201</v>
+      </c>
+      <c r="G33" s="14">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9F2B4-31D6-4C55-BAC0-7D448A9FC534}">
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -5149,13 +6738,13 @@
         <v>7</v>
       </c>
       <c r="E2" s="9">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="F2" s="9">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="G2" s="9">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -5172,13 +6761,13 @@
         <v>7</v>
       </c>
       <c r="E3" s="9">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="F3" s="9">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="G3" s="9">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -5195,13 +6784,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="9">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="F4" s="9">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="G4" s="9">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -5218,13 +6807,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="9">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="F5" s="9">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="G5" s="9">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -5241,13 +6830,13 @@
         <v>7</v>
       </c>
       <c r="E6" s="9">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="F6" s="9">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="G6" s="9">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -5264,13 +6853,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="9">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="F7" s="9">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="G7" s="9">
-        <v>58</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -5287,13 +6876,13 @@
         <v>7</v>
       </c>
       <c r="E8" s="9">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="F8" s="9">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="G8" s="9">
-        <v>58</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -5310,13 +6899,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="9">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="F9" s="9">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="G9" s="9">
-        <v>58</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -5333,13 +6922,13 @@
         <v>7</v>
       </c>
       <c r="E10" s="9">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="F10" s="9">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="G10" s="9">
-        <v>61</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -5356,13 +6945,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="9">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="F11" s="9">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="G11" s="9">
-        <v>61</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -5379,13 +6968,13 @@
         <v>7</v>
       </c>
       <c r="E12" s="9">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="F12" s="9">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="G12" s="9">
-        <v>61</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -5402,13 +6991,13 @@
         <v>7</v>
       </c>
       <c r="E13" s="9">
-        <v>66.5</v>
+        <v>124.5</v>
       </c>
       <c r="F13" s="9">
-        <v>69.5</v>
+        <v>131.5</v>
       </c>
       <c r="G13" s="9">
-        <v>68.5</v>
+        <v>126.5</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -5425,13 +7014,13 @@
         <v>7</v>
       </c>
       <c r="E14" s="9">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="F14" s="9">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="G14" s="9">
-        <v>70</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -5448,13 +7037,13 @@
         <v>7</v>
       </c>
       <c r="E15" s="9">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="F15" s="9">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="G15" s="9">
-        <v>75</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -5471,13 +7060,13 @@
         <v>7</v>
       </c>
       <c r="E16" s="9">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="F16" s="9">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="G16" s="9">
-        <v>81</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -5494,13 +7083,13 @@
         <v>7</v>
       </c>
       <c r="E17" s="9">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="F17" s="9">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="G17" s="9">
-        <v>81</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -5517,13 +7106,13 @@
         <v>7</v>
       </c>
       <c r="E18" s="9">
-        <v>88</v>
+        <v>172</v>
       </c>
       <c r="F18" s="9">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="G18" s="9">
-        <v>90</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -5540,13 +7129,13 @@
         <v>7</v>
       </c>
       <c r="E19" s="9">
-        <v>103</v>
+        <v>203</v>
       </c>
       <c r="F19" s="9">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="G19" s="9">
-        <v>105</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -5563,13 +7152,13 @@
         <v>7</v>
       </c>
       <c r="E20" s="9">
-        <v>123</v>
+        <v>233</v>
       </c>
       <c r="F20" s="9">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="G20" s="9">
-        <v>125</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -5586,13 +7175,13 @@
         <v>7</v>
       </c>
       <c r="E21" s="9">
-        <v>133</v>
+        <v>246</v>
       </c>
       <c r="F21" s="9">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="G21" s="9">
-        <v>135</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -5609,13 +7198,13 @@
         <v>7</v>
       </c>
       <c r="E22" s="9">
-        <v>133</v>
+        <v>246</v>
       </c>
       <c r="F22" s="9">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="G22" s="9">
-        <v>135</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -5632,13 +7221,13 @@
         <v>7</v>
       </c>
       <c r="E23" s="9">
-        <v>133</v>
+        <v>246</v>
       </c>
       <c r="F23" s="9">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="G23" s="9">
-        <v>135</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -5655,13 +7244,13 @@
         <v>7</v>
       </c>
       <c r="E24" s="9">
-        <v>133</v>
+        <v>246</v>
       </c>
       <c r="F24" s="9">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="G24" s="9">
-        <v>135</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -5678,13 +7267,13 @@
         <v>7</v>
       </c>
       <c r="E25" s="9">
-        <v>146</v>
+        <v>283</v>
       </c>
       <c r="F25" s="9">
-        <v>149</v>
+        <v>290</v>
       </c>
       <c r="G25" s="9">
-        <v>148</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -5701,13 +7290,13 @@
         <v>7</v>
       </c>
       <c r="E26" s="9">
-        <v>153</v>
+        <v>298</v>
       </c>
       <c r="F26" s="9">
-        <v>156</v>
+        <v>305</v>
       </c>
       <c r="G26" s="9">
-        <v>155</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -5724,13 +7313,13 @@
         <v>7</v>
       </c>
       <c r="E27" s="9">
-        <v>198</v>
+        <v>358</v>
       </c>
       <c r="F27" s="9">
-        <v>201</v>
+        <v>365</v>
       </c>
       <c r="G27" s="9">
-        <v>200</v>
+        <v>360</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -5741,682 +7330,133 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="9">
-        <v>198</v>
-      </c>
-      <c r="F28" s="9">
-        <v>201</v>
-      </c>
-      <c r="G28" s="9">
-        <v>200</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9F2B4-31D6-4C55-BAC0-7D448A9FC534}">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="6">
-        <v>45860</v>
-      </c>
-      <c r="B2" s="6">
-        <v>45860</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="9">
-        <v>108</v>
-      </c>
-      <c r="F2" s="9">
-        <v>115</v>
-      </c>
-      <c r="G2" s="9">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
-        <v>45867</v>
-      </c>
-      <c r="B3" s="6">
-        <v>45867</v>
-      </c>
-      <c r="C3" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="9">
-        <v>108</v>
-      </c>
-      <c r="F3" s="9">
-        <v>115</v>
-      </c>
-      <c r="G3" s="9">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
-        <v>45874</v>
-      </c>
-      <c r="B4" s="6">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="9">
-        <v>108</v>
-      </c>
-      <c r="F4" s="9">
-        <v>115</v>
-      </c>
-      <c r="G4" s="9">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
-        <v>45881</v>
-      </c>
-      <c r="B5" s="6">
-        <v>45881</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="9">
-        <v>108</v>
-      </c>
-      <c r="F5" s="9">
-        <v>115</v>
-      </c>
-      <c r="G5" s="9">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
-        <v>45888</v>
-      </c>
-      <c r="B6" s="6">
-        <v>45888</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="9">
-        <v>108</v>
-      </c>
-      <c r="F6" s="9">
-        <v>115</v>
-      </c>
-      <c r="G6" s="9">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="6">
-        <v>45895</v>
-      </c>
-      <c r="B7" s="6">
-        <v>45895</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="9">
-        <v>107</v>
-      </c>
-      <c r="F7" s="9">
-        <v>114</v>
-      </c>
-      <c r="G7" s="9">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
-        <v>45902</v>
-      </c>
-      <c r="B8" s="6">
-        <v>45902</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="9">
-        <v>107</v>
-      </c>
-      <c r="F8" s="9">
-        <v>114</v>
-      </c>
-      <c r="G8" s="9">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="6">
-        <v>45909</v>
-      </c>
-      <c r="B9" s="6">
-        <v>45909</v>
-      </c>
-      <c r="C9" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="9">
-        <v>107</v>
-      </c>
-      <c r="F9" s="9">
-        <v>114</v>
-      </c>
-      <c r="G9" s="9">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="6">
-        <v>45916</v>
-      </c>
-      <c r="B10" s="6">
-        <v>45916</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="9">
-        <v>112</v>
-      </c>
-      <c r="F10" s="9">
-        <v>119</v>
-      </c>
-      <c r="G10" s="9">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="6">
-        <v>45923</v>
-      </c>
-      <c r="B11" s="6">
-        <v>45923</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="9">
-        <v>112</v>
-      </c>
-      <c r="F11" s="9">
-        <v>119</v>
-      </c>
-      <c r="G11" s="9">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="6">
-        <v>45930</v>
-      </c>
-      <c r="B12" s="6">
-        <v>45930</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="9">
-        <v>112</v>
-      </c>
-      <c r="F12" s="9">
-        <v>119</v>
-      </c>
-      <c r="G12" s="9">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="6">
-        <v>45944</v>
-      </c>
-      <c r="B13" s="6">
-        <v>45944</v>
-      </c>
-      <c r="C13" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="9">
-        <v>124.5</v>
-      </c>
-      <c r="F13" s="9">
-        <v>131.5</v>
-      </c>
-      <c r="G13" s="9">
-        <v>126.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="6">
-        <v>45951</v>
-      </c>
-      <c r="B14" s="6">
-        <v>45951</v>
-      </c>
-      <c r="C14" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="9">
-        <v>134</v>
-      </c>
-      <c r="F14" s="9">
-        <v>141</v>
-      </c>
-      <c r="G14" s="9">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="6">
-        <v>45958</v>
-      </c>
-      <c r="B15" s="6">
-        <v>45958</v>
-      </c>
-      <c r="C15" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="9">
-        <v>143</v>
-      </c>
-      <c r="F15" s="9">
-        <v>150</v>
-      </c>
-      <c r="G15" s="9">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="6">
-        <v>45965</v>
-      </c>
-      <c r="B16" s="6">
-        <v>45965</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="9">
-        <v>156</v>
-      </c>
-      <c r="F16" s="9">
-        <v>163</v>
-      </c>
-      <c r="G16" s="9">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="6">
-        <v>45972</v>
-      </c>
-      <c r="B17" s="6">
-        <v>45972</v>
-      </c>
-      <c r="C17" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="9">
-        <v>156</v>
-      </c>
-      <c r="F17" s="9">
-        <v>163</v>
-      </c>
-      <c r="G17" s="9">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="6">
-        <v>45979</v>
-      </c>
-      <c r="B18" s="6">
-        <v>45979</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="9">
-        <v>172</v>
-      </c>
-      <c r="F18" s="9">
-        <v>179</v>
-      </c>
-      <c r="G18" s="9">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="6">
-        <v>45986</v>
-      </c>
-      <c r="B19" s="6">
-        <v>45986</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="9">
-        <v>203</v>
-      </c>
-      <c r="F19" s="9">
-        <v>210</v>
-      </c>
-      <c r="G19" s="9">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="6">
-        <v>45993</v>
-      </c>
-      <c r="B20" s="6">
-        <v>45993</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="9">
-        <v>233</v>
-      </c>
-      <c r="F20" s="9">
-        <v>240</v>
-      </c>
-      <c r="G20" s="9">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="6">
-        <v>46000</v>
-      </c>
-      <c r="B21" s="6">
-        <v>46000</v>
-      </c>
-      <c r="C21" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="9">
-        <v>246</v>
-      </c>
-      <c r="F21" s="9">
-        <v>253</v>
-      </c>
-      <c r="G21" s="9">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="6">
-        <v>46007</v>
-      </c>
-      <c r="B22" s="6">
-        <v>46007</v>
-      </c>
-      <c r="C22" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="9">
-        <v>246</v>
-      </c>
-      <c r="F22" s="9">
-        <v>253</v>
-      </c>
-      <c r="G22" s="9">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="6">
-        <v>46014</v>
-      </c>
-      <c r="B23" s="6">
-        <v>46014</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="9">
-        <v>246</v>
-      </c>
-      <c r="F23" s="9">
-        <v>253</v>
-      </c>
-      <c r="G23" s="9">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="6">
-        <v>46021</v>
-      </c>
-      <c r="B24" s="6">
-        <v>46021</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="9">
-        <v>246</v>
-      </c>
-      <c r="F24" s="9">
-        <v>253</v>
-      </c>
-      <c r="G24" s="9">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
-        <v>46028</v>
-      </c>
-      <c r="B25" s="6">
-        <v>46028</v>
-      </c>
-      <c r="C25" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="9">
-        <v>283</v>
-      </c>
-      <c r="F25" s="9">
-        <v>290</v>
-      </c>
-      <c r="G25" s="9">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="10">
-        <v>46035</v>
-      </c>
-      <c r="B26" s="10">
-        <v>46035</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="9">
-        <v>298</v>
-      </c>
-      <c r="F26" s="9">
-        <v>305</v>
-      </c>
-      <c r="G26" s="9">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="10">
-        <v>46042</v>
-      </c>
-      <c r="B27" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C27" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="9">
-        <v>358</v>
-      </c>
-      <c r="F27" s="9">
-        <v>365</v>
-      </c>
-      <c r="G27" s="9">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="6">
-        <v>46049</v>
-      </c>
-      <c r="B28" s="6">
-        <v>46049</v>
-      </c>
-      <c r="C28" s="7">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="9">
         <v>378</v>
       </c>
       <c r="F28" s="9">
         <v>385</v>
       </c>
       <c r="G28" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="9">
+        <v>378</v>
+      </c>
+      <c r="F29" s="9">
+        <v>385</v>
+      </c>
+      <c r="G29" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="9">
+        <v>378</v>
+      </c>
+      <c r="F30" s="9">
+        <v>385</v>
+      </c>
+      <c r="G30" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="9">
+        <v>378</v>
+      </c>
+      <c r="F31" s="9">
+        <v>385</v>
+      </c>
+      <c r="G31" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="9">
+        <v>378</v>
+      </c>
+      <c r="F32" s="9">
+        <v>385</v>
+      </c>
+      <c r="G32" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="9">
+        <v>378</v>
+      </c>
+      <c r="F33" s="9">
+        <v>385</v>
+      </c>
+      <c r="G33" s="9">
         <v>380</v>
       </c>
     </row>

--- a/data/industry/CFM/OEM SSD.xlsx
+++ b/data/industry/CFM/OEM SSD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8E4438-F3FA-491A-B271-9CB8E15CE9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1FD0BE-E235-4DEF-ACA7-060A6C820DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -75,24 +75,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -105,7 +105,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -136,46 +136,46 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -457,19 +457,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +492,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -515,7 +515,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -538,7 +538,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -561,7 +561,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -584,7 +584,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -607,7 +607,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -630,7 +630,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -653,7 +653,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -676,7 +676,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -699,7 +699,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -722,7 +722,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -745,7 +745,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -768,7 +768,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -791,7 +791,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -814,7 +814,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -837,7 +837,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -860,7 +860,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -883,7 +883,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -906,7 +906,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -929,7 +929,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -952,7 +952,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -975,7 +975,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -998,7 +998,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1251,7 +1251,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1364,6 +1364,144 @@
       </c>
       <c r="G39" s="12">
         <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>62</v>
+      </c>
+      <c r="F40" s="12">
+        <v>66</v>
+      </c>
+      <c r="G40" s="12">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>62</v>
+      </c>
+      <c r="F41" s="12">
+        <v>66</v>
+      </c>
+      <c r="G41" s="12">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>62</v>
+      </c>
+      <c r="F42" s="12">
+        <v>66</v>
+      </c>
+      <c r="G42" s="12">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>62</v>
+      </c>
+      <c r="F43" s="12">
+        <v>66</v>
+      </c>
+      <c r="G43" s="12">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>62</v>
+      </c>
+      <c r="F44" s="12">
+        <v>66</v>
+      </c>
+      <c r="G44" s="12">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>62</v>
+      </c>
+      <c r="F45" s="12">
+        <v>66</v>
+      </c>
+      <c r="G45" s="12">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1374,19 +1512,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F473D36E-208F-4614-83B5-69AB6F33294E}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1409,7 +1547,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1432,7 +1570,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1455,7 +1593,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1478,7 +1616,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1501,7 +1639,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1524,7 +1662,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1547,7 +1685,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1570,7 +1708,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1593,7 +1731,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1616,7 +1754,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1639,7 +1777,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1662,7 +1800,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1685,7 +1823,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -1708,7 +1846,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -1731,7 +1869,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -1754,7 +1892,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -1777,7 +1915,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -1800,7 +1938,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -1823,7 +1961,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -1846,7 +1984,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -1869,7 +2007,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -1892,7 +2030,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -1915,7 +2053,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1938,7 +2076,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1961,7 +2099,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1984,7 +2122,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2007,7 +2145,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2030,7 +2168,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2053,7 +2191,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2076,7 +2214,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2099,7 +2237,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2122,7 +2260,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2145,7 +2283,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2168,7 +2306,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2191,7 +2329,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2214,7 +2352,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2237,7 +2375,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2260,7 +2398,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2280,6 +2418,144 @@
         <v>117</v>
       </c>
       <c r="G39" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>110</v>
+      </c>
+      <c r="F40" s="12">
+        <v>117</v>
+      </c>
+      <c r="G40" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>110</v>
+      </c>
+      <c r="F41" s="12">
+        <v>117</v>
+      </c>
+      <c r="G41" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>110</v>
+      </c>
+      <c r="F42" s="12">
+        <v>117</v>
+      </c>
+      <c r="G42" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>110</v>
+      </c>
+      <c r="F43" s="12">
+        <v>117</v>
+      </c>
+      <c r="G43" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>110</v>
+      </c>
+      <c r="F44" s="12">
+        <v>117</v>
+      </c>
+      <c r="G44" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>110</v>
+      </c>
+      <c r="F45" s="12">
+        <v>117</v>
+      </c>
+      <c r="G45" s="12">
         <v>115</v>
       </c>
     </row>
@@ -2291,19 +2567,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6C0178-E414-47B2-A630-84DA7232A61F}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2326,7 +2602,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2349,7 +2625,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -2372,7 +2648,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -2395,7 +2671,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -2418,7 +2694,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -2441,7 +2717,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -2464,7 +2740,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -2487,7 +2763,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -2510,7 +2786,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -2533,7 +2809,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -2556,7 +2832,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2579,7 +2855,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -2602,7 +2878,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -2625,7 +2901,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -2648,7 +2924,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -2671,7 +2947,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -2694,7 +2970,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2717,7 +2993,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2740,7 +3016,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2763,7 +3039,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2786,7 +3062,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2809,7 +3085,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2832,7 +3108,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2855,7 +3131,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2878,7 +3154,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2901,7 +3177,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2924,7 +3200,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2947,7 +3223,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2970,7 +3246,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2993,7 +3269,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3016,7 +3292,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3039,7 +3315,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3062,7 +3338,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3085,7 +3361,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3108,7 +3384,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3131,7 +3407,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3154,7 +3430,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3177,7 +3453,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3197,6 +3473,144 @@
         <v>192</v>
       </c>
       <c r="G39" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>188</v>
+      </c>
+      <c r="F40" s="12">
+        <v>192</v>
+      </c>
+      <c r="G40" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>188</v>
+      </c>
+      <c r="F41" s="12">
+        <v>192</v>
+      </c>
+      <c r="G41" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>188</v>
+      </c>
+      <c r="F42" s="12">
+        <v>192</v>
+      </c>
+      <c r="G42" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>188</v>
+      </c>
+      <c r="F43" s="12">
+        <v>192</v>
+      </c>
+      <c r="G43" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>188</v>
+      </c>
+      <c r="F44" s="12">
+        <v>192</v>
+      </c>
+      <c r="G44" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>188</v>
+      </c>
+      <c r="F45" s="12">
+        <v>192</v>
+      </c>
+      <c r="G45" s="12">
         <v>190</v>
       </c>
     </row>
@@ -3208,19 +3622,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE21688-DF7E-4F8C-887E-342649A09FB0}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3243,7 +3657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3266,7 +3680,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3289,7 +3703,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3312,7 +3726,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3335,7 +3749,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3358,7 +3772,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3381,7 +3795,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3404,7 +3818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3427,7 +3841,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3450,7 +3864,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3473,7 +3887,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3496,7 +3910,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3519,7 +3933,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3542,7 +3956,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3565,7 +3979,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3588,7 +4002,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3611,7 +4025,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3634,7 +4048,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3657,7 +4071,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3680,7 +4094,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3703,7 +4117,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3726,7 +4140,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3749,7 +4163,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3772,7 +4186,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3795,7 +4209,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3818,7 +4232,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3841,7 +4255,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3864,7 +4278,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3887,7 +4301,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3910,7 +4324,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3933,7 +4347,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3956,7 +4370,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3979,7 +4393,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4002,7 +4416,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4025,7 +4439,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -4048,7 +4462,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -4071,7 +4485,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -4094,7 +4508,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -4115,6 +4529,144 @@
       </c>
       <c r="G39" s="12">
         <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>66.5</v>
+      </c>
+      <c r="F40" s="12">
+        <v>69</v>
+      </c>
+      <c r="G40" s="12">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>66.5</v>
+      </c>
+      <c r="F41" s="12">
+        <v>69</v>
+      </c>
+      <c r="G41" s="12">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>66.5</v>
+      </c>
+      <c r="F42" s="12">
+        <v>69</v>
+      </c>
+      <c r="G42" s="12">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>66.5</v>
+      </c>
+      <c r="F43" s="12">
+        <v>69</v>
+      </c>
+      <c r="G43" s="12">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>66.5</v>
+      </c>
+      <c r="F44" s="12">
+        <v>69</v>
+      </c>
+      <c r="G44" s="12">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>66.5</v>
+      </c>
+      <c r="F45" s="12">
+        <v>69</v>
+      </c>
+      <c r="G45" s="12">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4125,19 +4677,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{075E49D7-A50C-4EF3-8D98-3E3352C23834}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4160,7 +4712,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -4183,7 +4735,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -4206,7 +4758,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -4229,7 +4781,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -4252,7 +4804,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -4275,7 +4827,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -4298,7 +4850,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4321,7 +4873,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4344,7 +4896,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4367,7 +4919,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4390,7 +4942,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4413,7 +4965,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4436,7 +4988,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4459,7 +5011,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4482,7 +5034,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4505,7 +5057,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4528,7 +5080,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4551,7 +5103,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4574,7 +5126,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4597,7 +5149,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4620,7 +5172,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4643,7 +5195,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4666,7 +5218,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4689,7 +5241,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4712,7 +5264,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4735,7 +5287,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4758,7 +5310,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4781,7 +5333,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4804,7 +5356,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4827,7 +5379,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4850,7 +5402,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4873,7 +5425,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4896,7 +5448,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4919,7 +5471,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4942,7 +5494,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -4965,7 +5517,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -4988,7 +5540,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5011,7 +5563,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5031,6 +5583,144 @@
         <v>118</v>
       </c>
       <c r="G39" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F40" s="12">
+        <v>118</v>
+      </c>
+      <c r="G40" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F41" s="12">
+        <v>118</v>
+      </c>
+      <c r="G41" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F42" s="12">
+        <v>118</v>
+      </c>
+      <c r="G42" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F43" s="12">
+        <v>118</v>
+      </c>
+      <c r="G43" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F44" s="12">
+        <v>118</v>
+      </c>
+      <c r="G44" s="12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="F45" s="12">
+        <v>118</v>
+      </c>
+      <c r="G45" s="12">
         <v>115</v>
       </c>
     </row>
@@ -5042,19 +5732,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18515E64-A7B9-4EA8-8571-9A16CD6B2FD3}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5077,7 +5767,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -5100,7 +5790,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -5123,7 +5813,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -5146,7 +5836,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -5169,7 +5859,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -5192,7 +5882,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -5215,7 +5905,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -5238,7 +5928,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -5261,7 +5951,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -5284,7 +5974,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -5307,7 +5997,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -5330,7 +6020,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -5353,7 +6043,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -5376,7 +6066,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -5399,7 +6089,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -5422,7 +6112,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -5445,7 +6135,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -5468,7 +6158,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -5491,7 +6181,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -5514,7 +6204,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -5537,7 +6227,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -5560,7 +6250,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -5583,7 +6273,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -5606,7 +6296,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -5629,7 +6319,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -5652,7 +6342,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -5675,7 +6365,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -5698,7 +6388,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -5721,7 +6411,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -5744,7 +6434,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -5767,7 +6457,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -5790,7 +6480,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -5813,7 +6503,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -5836,7 +6526,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -5859,7 +6549,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -5882,7 +6572,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -5905,7 +6595,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5928,7 +6618,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5948,6 +6638,144 @@
         <v>192</v>
       </c>
       <c r="G39" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>189</v>
+      </c>
+      <c r="F40" s="12">
+        <v>192</v>
+      </c>
+      <c r="G40" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>189</v>
+      </c>
+      <c r="F41" s="12">
+        <v>192</v>
+      </c>
+      <c r="G41" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>189</v>
+      </c>
+      <c r="F42" s="12">
+        <v>192</v>
+      </c>
+      <c r="G42" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>189</v>
+      </c>
+      <c r="F43" s="12">
+        <v>192</v>
+      </c>
+      <c r="G43" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>189</v>
+      </c>
+      <c r="F44" s="12">
+        <v>192</v>
+      </c>
+      <c r="G44" s="12">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>189</v>
+      </c>
+      <c r="F45" s="12">
+        <v>192</v>
+      </c>
+      <c r="G45" s="12">
         <v>190</v>
       </c>
     </row>
@@ -5959,19 +6787,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8286ED8B-68EC-4D79-8787-976F03BA0C32}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5994,7 +6822,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6017,7 +6845,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6040,7 +6868,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6063,7 +6891,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -6086,7 +6914,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -6109,7 +6937,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -6132,7 +6960,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -6155,7 +6983,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -6178,7 +7006,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -6201,7 +7029,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -6224,7 +7052,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -6247,7 +7075,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -6270,7 +7098,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -6293,7 +7121,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -6316,7 +7144,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -6339,7 +7167,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -6362,7 +7190,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -6385,7 +7213,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -6408,7 +7236,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -6431,7 +7259,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -6454,7 +7282,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -6477,7 +7305,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -6500,7 +7328,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -6523,7 +7351,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -6546,7 +7374,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -6569,7 +7397,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -6592,7 +7420,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -6615,7 +7443,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -6638,7 +7466,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -6661,7 +7489,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -6684,7 +7512,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -6707,7 +7535,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -6730,7 +7558,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -6753,7 +7581,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -6776,7 +7604,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -6799,7 +7627,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -6822,7 +7650,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -6845,7 +7673,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -6865,6 +7693,144 @@
         <v>120</v>
       </c>
       <c r="G39" s="12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>116</v>
+      </c>
+      <c r="F40" s="12">
+        <v>120</v>
+      </c>
+      <c r="G40" s="12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>116</v>
+      </c>
+      <c r="F41" s="12">
+        <v>120</v>
+      </c>
+      <c r="G41" s="12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>116</v>
+      </c>
+      <c r="F42" s="12">
+        <v>120</v>
+      </c>
+      <c r="G42" s="12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>116</v>
+      </c>
+      <c r="F43" s="12">
+        <v>120</v>
+      </c>
+      <c r="G43" s="12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>116</v>
+      </c>
+      <c r="F44" s="12">
+        <v>120</v>
+      </c>
+      <c r="G44" s="12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>116</v>
+      </c>
+      <c r="F45" s="12">
+        <v>120</v>
+      </c>
+      <c r="G45" s="12">
         <v>118</v>
       </c>
     </row>
@@ -6876,19 +7842,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62752974-E8DF-439D-ACF9-ECD10A65F3F8}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6911,7 +7877,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6934,7 +7900,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6957,7 +7923,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6980,7 +7946,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -7003,7 +7969,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -7026,7 +7992,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -7049,7 +8015,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -7072,7 +8038,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -7095,7 +8061,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -7118,7 +8084,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -7141,7 +8107,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -7164,7 +8130,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -7187,7 +8153,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -7210,7 +8176,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -7233,7 +8199,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -7256,7 +8222,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -7279,7 +8245,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -7302,7 +8268,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -7325,7 +8291,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -7348,7 +8314,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -7371,7 +8337,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -7394,7 +8360,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -7417,7 +8383,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -7440,7 +8406,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -7463,7 +8429,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -7486,7 +8452,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -7509,7 +8475,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -7532,7 +8498,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -7555,7 +8521,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -7578,7 +8544,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -7601,7 +8567,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -7624,7 +8590,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -7647,7 +8613,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -7670,7 +8636,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -7693,7 +8659,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -7716,7 +8682,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -7739,7 +8705,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -7762,7 +8728,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -7782,6 +8748,144 @@
         <v>201</v>
       </c>
       <c r="G39" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="14">
+        <v>198</v>
+      </c>
+      <c r="F40" s="14">
+        <v>201</v>
+      </c>
+      <c r="G40" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="14">
+        <v>198</v>
+      </c>
+      <c r="F41" s="14">
+        <v>201</v>
+      </c>
+      <c r="G41" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="14">
+        <v>198</v>
+      </c>
+      <c r="F42" s="14">
+        <v>201</v>
+      </c>
+      <c r="G42" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="14">
+        <v>198</v>
+      </c>
+      <c r="F43" s="14">
+        <v>201</v>
+      </c>
+      <c r="G43" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="14">
+        <v>198</v>
+      </c>
+      <c r="F44" s="14">
+        <v>201</v>
+      </c>
+      <c r="G44" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="14">
+        <v>198</v>
+      </c>
+      <c r="F45" s="14">
+        <v>201</v>
+      </c>
+      <c r="G45" s="14">
         <v>200</v>
       </c>
     </row>
@@ -7793,19 +8897,19 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9F2B4-31D6-4C55-BAC0-7D448A9FC534}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7828,7 +8932,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -7851,7 +8955,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -7874,7 +8978,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -7897,7 +9001,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -7920,7 +9024,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -7943,7 +9047,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -7966,7 +9070,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -7989,7 +9093,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -8012,7 +9116,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -8035,7 +9139,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -8058,7 +9162,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -8081,7 +9185,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -8104,7 +9208,7 @@
         <v>126.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -8127,7 +9231,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -8150,7 +9254,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -8173,7 +9277,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -8196,7 +9300,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -8219,7 +9323,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -8242,7 +9346,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -8265,7 +9369,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -8288,7 +9392,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -8311,7 +9415,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -8334,7 +9438,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -8357,7 +9461,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -8380,7 +9484,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -8403,7 +9507,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -8426,7 +9530,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -8449,7 +9553,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -8472,7 +9576,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -8495,7 +9599,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -8518,7 +9622,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -8541,7 +9645,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -8564,7 +9668,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -8587,7 +9691,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -8610,7 +9714,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -8633,7 +9737,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -8656,7 +9760,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -8679,7 +9783,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -8699,6 +9803,144 @@
         <v>385</v>
       </c>
       <c r="G39" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="9">
+        <v>378</v>
+      </c>
+      <c r="F40" s="9">
+        <v>385</v>
+      </c>
+      <c r="G40" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="9">
+        <v>378</v>
+      </c>
+      <c r="F41" s="9">
+        <v>385</v>
+      </c>
+      <c r="G41" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="9">
+        <v>378</v>
+      </c>
+      <c r="F42" s="9">
+        <v>385</v>
+      </c>
+      <c r="G42" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="9">
+        <v>378</v>
+      </c>
+      <c r="F43" s="9">
+        <v>385</v>
+      </c>
+      <c r="G43" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="9">
+        <v>378</v>
+      </c>
+      <c r="F44" s="9">
+        <v>385</v>
+      </c>
+      <c r="G44" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="9">
+        <v>378</v>
+      </c>
+      <c r="F45" s="9">
+        <v>385</v>
+      </c>
+      <c r="G45" s="9">
         <v>380</v>
       </c>
     </row>
